--- a/exemple-ePrescription/ig/StructureDefinition-fr-lm-participant.xlsx
+++ b/exemple-ePrescription/ig/StructureDefinition-fr-lm-participant.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="109">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T11:50:30+00:00</t>
+    <t>2026-06-01T14:06:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,7 +250,27 @@
     <t>Base</t>
   </si>
   <si>
-    <t>fr-lm-participant.typeParticipation</t>
+    <t>fr-lm-participant.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Identifiants de la personne</t>
+  </si>
+  <si>
+    <t>fr-lm-participant.name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-human-name
+</t>
+  </si>
+  <si>
+    <t>Nom de la personne</t>
+  </si>
+  <si>
+    <t>fr-lm-participant.type</t>
   </si>
   <si>
     <t>1</t>
@@ -260,33 +280,75 @@
 </t>
   </si>
   <si>
-    <t>Type de participation.</t>
-  </si>
-  <si>
-    <t>fr-lm-participant.roleFonctionnel</t>
-  </si>
-  <si>
-    <t>Rôle fonctionnel.</t>
-  </si>
-  <si>
-    <t>fr-lm-participant.dateDebutEtOuFinParticipation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ParticipationType-cisis (2.16.840.1.113883.1.11.10901)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ParticipationType-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-participant.role</t>
+  </si>
+  <si>
+    <t>Rôle fonctionnel</t>
+  </si>
+  <si>
+    <t>JDV_J47_FunctionCode_CISIS (1.2.250.1.213.1.1.5.124)</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J47-FunctionCode-CISIS/FHIR/JDV-J47-FunctionCode-CISIS</t>
+  </si>
+  <si>
+    <t>fr-lm-participant.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
 </t>
   </si>
   <si>
-    <t>Date de début et/ou de fin de la participation.</t>
+    <t>Période de la participation</t>
   </si>
   <si>
     <t>fr-lm-participant.participant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
+    <t xml:space="preserve">Base
 </t>
   </si>
   <si>
     <t>Participant</t>
+  </si>
+  <si>
+    <t>fr-lm-participant.participant.participantProfessional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-participant.participant.participantOrganisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-participant.participant.participantDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
+</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
   </si>
 </sst>
 </file>
@@ -588,11 +650,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ6"/>
+  <dimension ref="A1:AJ11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="38.625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="41.8671875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="41.8671875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -601,7 +663,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="73.859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="73.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -615,14 +677,14 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="53.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="74.6015625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="41.8671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
@@ -851,28 +913,28 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H3" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I3" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J3" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K3" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="G3" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H3" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I3" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J3" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K3" t="s" s="2">
+      <c r="L3" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="L3" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="M3" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -926,10 +988,10 @@
         <v>78</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>73</v>
@@ -940,10 +1002,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -954,7 +1016,7 @@
         <v>74</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>73</v>
@@ -966,7 +1028,7 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>83</v>
@@ -1023,13 +1085,13 @@
         <v>73</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>73</v>
@@ -1051,10 +1113,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>73</v>
@@ -1066,13 +1128,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1102,10 +1164,10 @@
         <v>73</v>
       </c>
       <c r="Y5" t="s" s="2">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="Z5" t="s" s="2">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="AA5" t="s" s="2">
         <v>73</v>
@@ -1126,10 +1188,10 @@
         <v>84</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>73</v>
@@ -1140,10 +1202,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1151,10 +1213,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -1166,13 +1228,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1202,10 +1264,10 @@
         <v>73</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>73</v>
@@ -1223,18 +1285,518 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ6" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q9" s="2"/>
+      <c r="R9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH10" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI10" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="D11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K11" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q11" s="2"/>
+      <c r="R11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF11" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AG11" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH11" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ11" t="s" s="2">
         <v>73</v>
       </c>
     </row>
